--- a/hackton_exercicio/limpo/despesas_limpo.xlsx
+++ b/hackton_exercicio/limpo/despesas_limpo.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,42 +421,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id_despesas</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tipo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>setor</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>fornecedor</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>trimestre</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>mensal</t>
         </is>
@@ -478,7 +466,7 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="1" t="n">
         <v>45522</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -510,7 +498,7 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="1" t="n">
         <v>45550</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -542,7 +530,7 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="1" t="n">
         <v>45526</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -574,7 +562,7 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="1" t="n">
         <v>45537</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -606,7 +594,7 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="1" t="n">
         <v>45690</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -638,7 +626,7 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="1" t="n">
         <v>45665</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -670,7 +658,7 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="1" t="n">
         <v>45511</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -702,7 +690,7 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="1" t="n">
         <v>45514</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -734,7 +722,7 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="1" t="n">
         <v>45462</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,7 +754,7 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="1" t="n">
         <v>45686</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -798,7 +786,7 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="1" t="n">
         <v>45701</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -830,7 +818,7 @@
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="1" t="n">
         <v>45589</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -862,7 +850,7 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="1" t="n">
         <v>45503</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -894,7 +882,7 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="1" t="n">
         <v>45783</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -926,7 +914,7 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="1" t="n">
         <v>45686</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -958,7 +946,7 @@
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" s="1" t="n">
         <v>45693</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -984,7 +972,7 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="1" t="n">
         <v>45462</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -1012,7 +1000,7 @@
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" s="1" t="n">
         <v>45540</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -1044,7 +1032,7 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -1076,7 +1064,7 @@
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" s="1" t="n">
         <v>45441</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -1108,7 +1096,7 @@
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" s="1" t="n">
         <v>45780</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -1140,7 +1128,7 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" s="1" t="n">
         <v>45481</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -1172,7 +1160,7 @@
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B24" s="1" t="n">
         <v>45750</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -1204,7 +1192,7 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B25" s="1" t="n">
         <v>45582</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -1236,7 +1224,7 @@
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B26" s="1" t="n">
         <v>45578</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -1268,7 +1256,7 @@
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="B27" s="1" t="n">
         <v>45431</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -1300,7 +1288,7 @@
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" s="1" t="n">
         <v>45516</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -1330,7 +1318,7 @@
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" s="1" t="n">
         <v>45714</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -1362,7 +1350,7 @@
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B30" s="1" t="n">
         <v>45466</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -1394,7 +1382,7 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B31" s="1" t="n">
         <v>45694</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -1426,7 +1414,7 @@
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B32" s="1" t="n">
         <v>45687</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -1458,7 +1446,7 @@
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B33" s="1" t="n">
         <v>45561</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -1490,7 +1478,7 @@
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B34" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -1522,7 +1510,7 @@
       <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="n">
+      <c r="B35" s="1" t="n">
         <v>45720</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -1554,7 +1542,7 @@
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B36" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -1586,7 +1574,7 @@
       <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B37" s="1" t="n">
         <v>45719</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -1618,7 +1606,7 @@
       <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B38" s="1" t="n">
         <v>45605</v>
       </c>
       <c r="C38" t="inlineStr">
@@ -1650,7 +1638,7 @@
       <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="n">
+      <c r="B39" s="1" t="n">
         <v>45694</v>
       </c>
       <c r="C39" t="inlineStr">
@@ -1680,7 +1668,7 @@
       <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="n">
+      <c r="B40" s="1" t="n">
         <v>45525</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -1712,7 +1700,7 @@
       <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="n">
+      <c r="B41" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -1744,7 +1732,7 @@
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B42" s="1" t="n">
         <v>45734</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -1776,7 +1764,7 @@
       <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="n">
+      <c r="B43" s="1" t="n">
         <v>45635</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -1808,7 +1796,7 @@
       <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="n">
+      <c r="B44" s="1" t="n">
         <v>45726</v>
       </c>
       <c r="C44" t="inlineStr">
@@ -1840,7 +1828,7 @@
       <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="n">
+      <c r="B45" s="1" t="n">
         <v>45691</v>
       </c>
       <c r="C45" t="inlineStr">
@@ -1872,7 +1860,7 @@
       <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="n">
+      <c r="B46" s="1" t="n">
         <v>45554</v>
       </c>
       <c r="C46" t="inlineStr">
@@ -1904,7 +1892,7 @@
       <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="n">
+      <c r="B47" s="1" t="n">
         <v>45518</v>
       </c>
       <c r="C47" t="inlineStr">
@@ -1932,7 +1920,7 @@
       <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="n">
+      <c r="B48" s="1" t="n">
         <v>45520</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -1964,7 +1952,7 @@
       <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="n">
+      <c r="B49" s="1" t="n">
         <v>45551</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -1996,7 +1984,7 @@
       <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="n">
+      <c r="B50" s="1" t="n">
         <v>45766</v>
       </c>
       <c r="C50" t="inlineStr">
@@ -2024,7 +2012,7 @@
       <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="n">
+      <c r="B51" s="1" t="n">
         <v>45493</v>
       </c>
       <c r="C51" t="inlineStr">
@@ -2056,7 +2044,7 @@
       <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="n">
+      <c r="B52" s="1" t="n">
         <v>45534</v>
       </c>
       <c r="C52" t="inlineStr">
@@ -2088,7 +2076,7 @@
       <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="n">
+      <c r="B53" s="1" t="n">
         <v>45646</v>
       </c>
       <c r="C53" t="inlineStr">
@@ -2116,7 +2104,7 @@
       <c r="A54" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="n">
+      <c r="B54" s="1" t="n">
         <v>45741</v>
       </c>
       <c r="C54" t="inlineStr">
@@ -2148,7 +2136,7 @@
       <c r="A55" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="n">
+      <c r="B55" s="1" t="n">
         <v>45578</v>
       </c>
       <c r="C55" t="inlineStr">
@@ -2180,7 +2168,7 @@
       <c r="A56" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="2" t="n">
+      <c r="B56" s="1" t="n">
         <v>45774</v>
       </c>
       <c r="C56" t="inlineStr">
@@ -2212,7 +2200,7 @@
       <c r="A57" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="2" t="n">
+      <c r="B57" s="1" t="n">
         <v>45714</v>
       </c>
       <c r="C57" t="inlineStr">
@@ -2240,7 +2228,7 @@
       <c r="A58" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="2" t="n">
+      <c r="B58" s="1" t="n">
         <v>45442</v>
       </c>
       <c r="C58" t="inlineStr">
@@ -2272,7 +2260,7 @@
       <c r="A59" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="2" t="n">
+      <c r="B59" s="1" t="n">
         <v>45673</v>
       </c>
       <c r="C59" t="inlineStr">
@@ -2304,7 +2292,7 @@
       <c r="A60" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="2" t="n">
+      <c r="B60" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="C60" t="inlineStr">
@@ -2336,7 +2324,7 @@
       <c r="A61" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="2" t="n">
+      <c r="B61" s="1" t="n">
         <v>45659</v>
       </c>
       <c r="C61" t="inlineStr">
@@ -2368,7 +2356,7 @@
       <c r="A62" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="2" t="n">
+      <c r="B62" s="1" t="n">
         <v>45727</v>
       </c>
       <c r="C62" t="inlineStr">
@@ -2400,7 +2388,7 @@
       <c r="A63" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="2" t="n">
+      <c r="B63" s="1" t="n">
         <v>45531</v>
       </c>
       <c r="C63" t="inlineStr">
@@ -2432,7 +2420,7 @@
       <c r="A64" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="n">
+      <c r="B64" s="1" t="n">
         <v>45542</v>
       </c>
       <c r="C64" t="inlineStr">
@@ -2464,7 +2452,7 @@
       <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="2" t="n">
+      <c r="B65" s="1" t="n">
         <v>45729</v>
       </c>
       <c r="C65" t="inlineStr">
@@ -2496,7 +2484,7 @@
       <c r="A66" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="2" t="n">
+      <c r="B66" s="1" t="n">
         <v>45578</v>
       </c>
       <c r="C66" t="inlineStr">
@@ -2528,7 +2516,7 @@
       <c r="A67" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="2" t="n">
+      <c r="B67" s="1" t="n">
         <v>45571</v>
       </c>
       <c r="C67" t="inlineStr">
@@ -2560,7 +2548,7 @@
       <c r="A68" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="2" t="n">
+      <c r="B68" s="1" t="n">
         <v>45660</v>
       </c>
       <c r="C68" t="inlineStr">
@@ -2592,7 +2580,7 @@
       <c r="A69" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="2" t="n">
+      <c r="B69" s="1" t="n">
         <v>45594</v>
       </c>
       <c r="C69" t="inlineStr">
@@ -2624,7 +2612,7 @@
       <c r="A70" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="2" t="n">
+      <c r="B70" s="1" t="n">
         <v>45723</v>
       </c>
       <c r="C70" t="inlineStr">
@@ -2656,7 +2644,7 @@
       <c r="A71" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="2" t="n">
+      <c r="B71" s="1" t="n">
         <v>45769</v>
       </c>
       <c r="C71" t="inlineStr">
@@ -2688,7 +2676,7 @@
       <c r="A72" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="2" t="n">
+      <c r="B72" s="1" t="n">
         <v>45594</v>
       </c>
       <c r="C72" t="inlineStr">
@@ -2720,7 +2708,7 @@
       <c r="A73" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="2" t="n">
+      <c r="B73" s="1" t="n">
         <v>45690</v>
       </c>
       <c r="C73" t="inlineStr">
@@ -2748,7 +2736,7 @@
       <c r="A74" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="2" t="n">
+      <c r="B74" s="1" t="n">
         <v>45774</v>
       </c>
       <c r="C74" t="inlineStr">
@@ -2780,7 +2768,7 @@
       <c r="A75" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="2" t="n">
+      <c r="B75" s="1" t="n">
         <v>45543</v>
       </c>
       <c r="C75" t="inlineStr">
@@ -2810,7 +2798,7 @@
       <c r="A76" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="2" t="n">
+      <c r="B76" s="1" t="n">
         <v>45481</v>
       </c>
       <c r="C76" t="inlineStr">
@@ -2838,7 +2826,7 @@
       <c r="A77" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="2" t="n">
+      <c r="B77" s="1" t="n">
         <v>45531</v>
       </c>
       <c r="C77" t="inlineStr">
@@ -2870,7 +2858,7 @@
       <c r="A78" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="2" t="n">
+      <c r="B78" s="1" t="n">
         <v>45634</v>
       </c>
       <c r="C78" t="inlineStr">
@@ -2902,7 +2890,7 @@
       <c r="A79" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="2" t="n">
+      <c r="B79" s="1" t="n">
         <v>45480</v>
       </c>
       <c r="C79" t="inlineStr">
@@ -2934,7 +2922,7 @@
       <c r="A80" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="2" t="n">
+      <c r="B80" s="1" t="n">
         <v>45462</v>
       </c>
       <c r="C80" t="inlineStr">
@@ -2966,7 +2954,7 @@
       <c r="A81" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="2" t="n">
+      <c r="B81" s="1" t="n">
         <v>45691</v>
       </c>
       <c r="C81" t="inlineStr">
@@ -2998,7 +2986,7 @@
       <c r="A82" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="2" t="n">
+      <c r="B82" s="1" t="n">
         <v>45678</v>
       </c>
       <c r="C82" t="inlineStr">
@@ -3026,7 +3014,7 @@
       <c r="A83" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="2" t="n">
+      <c r="B83" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="C83" t="inlineStr">
@@ -3058,7 +3046,7 @@
       <c r="A84" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="2" t="n">
+      <c r="B84" s="1" t="n">
         <v>45707</v>
       </c>
       <c r="C84" t="inlineStr">
@@ -3090,7 +3078,7 @@
       <c r="A85" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="2" t="n">
+      <c r="B85" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="C85" t="inlineStr">
@@ -3118,7 +3106,7 @@
       <c r="A86" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="2" t="n">
+      <c r="B86" s="1" t="n">
         <v>45461</v>
       </c>
       <c r="C86" t="inlineStr">
@@ -3150,7 +3138,7 @@
       <c r="A87" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="2" t="n">
+      <c r="B87" s="1" t="n">
         <v>45737</v>
       </c>
       <c r="C87" t="inlineStr">
@@ -3182,7 +3170,7 @@
       <c r="A88" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="2" t="n">
+      <c r="B88" s="1" t="n">
         <v>45618</v>
       </c>
       <c r="C88" t="inlineStr">
@@ -3214,7 +3202,7 @@
       <c r="A89" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="2" t="n">
+      <c r="B89" s="1" t="n">
         <v>45516</v>
       </c>
       <c r="C89" t="inlineStr">
@@ -3246,7 +3234,7 @@
       <c r="A90" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="2" t="n">
+      <c r="B90" s="1" t="n">
         <v>45765</v>
       </c>
       <c r="C90" t="inlineStr">
@@ -3278,7 +3266,7 @@
       <c r="A91" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="2" t="n">
+      <c r="B91" s="1" t="n">
         <v>45649</v>
       </c>
       <c r="C91" t="inlineStr">
@@ -3310,7 +3298,7 @@
       <c r="A92" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="2" t="n">
+      <c r="B92" s="1" t="n">
         <v>45452</v>
       </c>
       <c r="C92" t="inlineStr">
@@ -3336,7 +3324,7 @@
       <c r="A93" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="2" t="n">
+      <c r="B93" s="1" t="n">
         <v>45470</v>
       </c>
       <c r="C93" t="inlineStr">
@@ -3364,7 +3352,7 @@
       <c r="A94" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="2" t="n">
+      <c r="B94" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="C94" t="inlineStr">
@@ -3396,7 +3384,7 @@
       <c r="A95" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="2" t="n">
+      <c r="B95" s="1" t="n">
         <v>45758</v>
       </c>
       <c r="C95" t="inlineStr">
@@ -3428,7 +3416,7 @@
       <c r="A96" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="2" t="n">
+      <c r="B96" s="1" t="n">
         <v>45553</v>
       </c>
       <c r="C96" t="inlineStr">
@@ -3460,7 +3448,7 @@
       <c r="A97" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="2" t="n">
+      <c r="B97" s="1" t="n">
         <v>45462</v>
       </c>
       <c r="C97" t="inlineStr">
@@ -3492,7 +3480,7 @@
       <c r="A98" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="2" t="n">
+      <c r="B98" s="1" t="n">
         <v>45430</v>
       </c>
       <c r="C98" t="inlineStr">
@@ -3524,7 +3512,7 @@
       <c r="A99" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="2" t="n">
+      <c r="B99" s="1" t="n">
         <v>45542</v>
       </c>
       <c r="C99" t="inlineStr">
@@ -3556,7 +3544,7 @@
       <c r="A100" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="2" t="n">
+      <c r="B100" s="1" t="n">
         <v>45679</v>
       </c>
       <c r="C100" t="inlineStr">
@@ -3588,7 +3576,7 @@
       <c r="A101" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="2" t="n">
+      <c r="B101" s="1" t="n">
         <v>45595</v>
       </c>
       <c r="C101" t="inlineStr">
@@ -3620,7 +3608,7 @@
       <c r="A102" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="2" t="n">
+      <c r="B102" s="1" t="n">
         <v>45533</v>
       </c>
       <c r="C102" t="inlineStr">
@@ -3652,7 +3640,7 @@
       <c r="A103" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="2" t="n">
+      <c r="B103" s="1" t="n">
         <v>45754</v>
       </c>
       <c r="C103" t="inlineStr">
@@ -3684,7 +3672,7 @@
       <c r="A104" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="2" t="n">
+      <c r="B104" s="1" t="n">
         <v>45449</v>
       </c>
       <c r="C104" t="inlineStr">
@@ -3716,7 +3704,7 @@
       <c r="A105" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="2" t="n">
+      <c r="B105" s="1" t="n">
         <v>45595</v>
       </c>
       <c r="C105" t="inlineStr">
@@ -3748,7 +3736,7 @@
       <c r="A106" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="2" t="n">
+      <c r="B106" s="1" t="n">
         <v>45563</v>
       </c>
       <c r="C106" t="inlineStr">
@@ -3780,7 +3768,7 @@
       <c r="A107" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="2" t="n">
+      <c r="B107" s="1" t="n">
         <v>45420</v>
       </c>
       <c r="C107" t="inlineStr">
@@ -3812,7 +3800,7 @@
       <c r="A108" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="2" t="n">
+      <c r="B108" s="1" t="n">
         <v>45458</v>
       </c>
       <c r="C108" t="inlineStr">
@@ -3844,7 +3832,7 @@
       <c r="A109" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="2" t="n">
+      <c r="B109" s="1" t="n">
         <v>45647</v>
       </c>
       <c r="C109" t="inlineStr">
@@ -3876,7 +3864,7 @@
       <c r="A110" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="2" t="n">
+      <c r="B110" s="1" t="n">
         <v>45718</v>
       </c>
       <c r="C110" t="inlineStr">
@@ -3908,7 +3896,7 @@
       <c r="A111" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="2" t="n">
+      <c r="B111" s="1" t="n">
         <v>45710</v>
       </c>
       <c r="C111" t="inlineStr">
@@ -3938,7 +3926,7 @@
       <c r="A112" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="2" t="n">
+      <c r="B112" s="1" t="n">
         <v>45610</v>
       </c>
       <c r="C112" t="inlineStr">
@@ -3970,7 +3958,7 @@
       <c r="A113" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="2" t="n">
+      <c r="B113" s="1" t="n">
         <v>45547</v>
       </c>
       <c r="C113" t="inlineStr">
@@ -4002,7 +3990,7 @@
       <c r="A114" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="2" t="n">
+      <c r="B114" s="1" t="n">
         <v>45771</v>
       </c>
       <c r="C114" t="inlineStr">
@@ -4034,7 +4022,7 @@
       <c r="A115" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="2" t="n">
+      <c r="B115" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="C115" t="inlineStr">
@@ -4066,7 +4054,7 @@
       <c r="A116" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="2" t="n">
+      <c r="B116" s="1" t="n">
         <v>45704</v>
       </c>
       <c r="C116" t="inlineStr">
@@ -4098,7 +4086,7 @@
       <c r="A117" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="2" t="n">
+      <c r="B117" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="C117" t="inlineStr">
@@ -4130,7 +4118,7 @@
       <c r="A118" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="2" t="n">
+      <c r="B118" s="1" t="n">
         <v>45732</v>
       </c>
       <c r="C118" t="inlineStr">
@@ -4162,7 +4150,7 @@
       <c r="A119" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="2" t="n">
+      <c r="B119" s="1" t="n">
         <v>45459</v>
       </c>
       <c r="C119" t="inlineStr">
@@ -4194,7 +4182,7 @@
       <c r="A120" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="2" t="n">
+      <c r="B120" s="1" t="n">
         <v>45583</v>
       </c>
       <c r="C120" t="inlineStr">
@@ -4226,7 +4214,7 @@
       <c r="A121" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="2" t="n">
+      <c r="B121" s="1" t="n">
         <v>45705</v>
       </c>
       <c r="C121" t="inlineStr">
@@ -4254,7 +4242,7 @@
       <c r="A122" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="2" t="n">
+      <c r="B122" s="1" t="n">
         <v>45469</v>
       </c>
       <c r="C122" t="inlineStr">
@@ -4286,7 +4274,7 @@
       <c r="A123" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="2" t="n">
+      <c r="B123" s="1" t="n">
         <v>45463</v>
       </c>
       <c r="C123" t="inlineStr">
@@ -4318,7 +4306,7 @@
       <c r="A124" t="n">
         <v>123</v>
       </c>
-      <c r="B124" s="2" t="n">
+      <c r="B124" s="1" t="n">
         <v>45588</v>
       </c>
       <c r="C124" t="inlineStr">
@@ -4346,7 +4334,7 @@
       <c r="A125" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="2" t="n">
+      <c r="B125" s="1" t="n">
         <v>45780</v>
       </c>
       <c r="C125" t="inlineStr">
@@ -4376,7 +4364,7 @@
       <c r="A126" t="n">
         <v>125</v>
       </c>
-      <c r="B126" s="2" t="n">
+      <c r="B126" s="1" t="n">
         <v>45736</v>
       </c>
       <c r="C126" t="inlineStr">
@@ -4408,7 +4396,7 @@
       <c r="A127" t="n">
         <v>126</v>
       </c>
-      <c r="B127" s="2" t="n">
+      <c r="B127" s="1" t="n">
         <v>45425</v>
       </c>
       <c r="C127" t="inlineStr">
@@ -4440,7 +4428,7 @@
       <c r="A128" t="n">
         <v>127</v>
       </c>
-      <c r="B128" s="2" t="n">
+      <c r="B128" s="1" t="n">
         <v>45589</v>
       </c>
       <c r="C128" t="inlineStr">
@@ -4472,7 +4460,7 @@
       <c r="A129" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="2" t="n">
+      <c r="B129" s="1" t="n">
         <v>45573</v>
       </c>
       <c r="C129" t="inlineStr">
@@ -4504,7 +4492,7 @@
       <c r="A130" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="2" t="n">
+      <c r="B130" s="1" t="n">
         <v>45587</v>
       </c>
       <c r="C130" t="inlineStr">
@@ -4536,7 +4524,7 @@
       <c r="A131" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="2" t="n">
+      <c r="B131" s="1" t="n">
         <v>45537</v>
       </c>
       <c r="C131" t="inlineStr">
@@ -4568,7 +4556,7 @@
       <c r="A132" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="2" t="n">
+      <c r="B132" s="1" t="n">
         <v>45463</v>
       </c>
       <c r="C132" t="inlineStr">
@@ -4600,7 +4588,7 @@
       <c r="A133" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="2" t="n">
+      <c r="B133" s="1" t="n">
         <v>45548</v>
       </c>
       <c r="C133" t="inlineStr">
@@ -4632,7 +4620,7 @@
       <c r="A134" t="n">
         <v>133</v>
       </c>
-      <c r="B134" s="2" t="n">
+      <c r="B134" s="1" t="n">
         <v>45707</v>
       </c>
       <c r="C134" t="inlineStr">
@@ -4664,7 +4652,7 @@
       <c r="A135" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="2" t="n">
+      <c r="B135" s="1" t="n">
         <v>45466</v>
       </c>
       <c r="C135" t="inlineStr">
@@ -4696,7 +4684,7 @@
       <c r="A136" t="n">
         <v>135</v>
       </c>
-      <c r="B136" s="2" t="n">
+      <c r="B136" s="1" t="n">
         <v>45462</v>
       </c>
       <c r="C136" t="inlineStr">
@@ -4724,7 +4712,7 @@
       <c r="A137" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="2" t="n">
+      <c r="B137" s="1" t="n">
         <v>45741</v>
       </c>
       <c r="C137" t="inlineStr">
@@ -4756,7 +4744,7 @@
       <c r="A138" t="n">
         <v>137</v>
       </c>
-      <c r="B138" s="2" t="n">
+      <c r="B138" s="1" t="n">
         <v>45507</v>
       </c>
       <c r="C138" t="inlineStr">
@@ -4788,7 +4776,7 @@
       <c r="A139" t="n">
         <v>138</v>
       </c>
-      <c r="B139" s="2" t="n">
+      <c r="B139" s="1" t="n">
         <v>45647</v>
       </c>
       <c r="C139" t="inlineStr">
@@ -4820,7 +4808,7 @@
       <c r="A140" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="2" t="n">
+      <c r="B140" s="1" t="n">
         <v>45768</v>
       </c>
       <c r="C140" t="inlineStr">
@@ -4852,7 +4840,7 @@
       <c r="A141" t="n">
         <v>140</v>
       </c>
-      <c r="B141" s="2" t="n">
+      <c r="B141" s="1" t="n">
         <v>45470</v>
       </c>
       <c r="C141" t="inlineStr">
@@ -4882,7 +4870,7 @@
       <c r="A142" t="n">
         <v>141</v>
       </c>
-      <c r="B142" s="2" t="n">
+      <c r="B142" s="1" t="n">
         <v>45741</v>
       </c>
       <c r="C142" t="inlineStr">
@@ -4914,7 +4902,7 @@
       <c r="A143" t="n">
         <v>142</v>
       </c>
-      <c r="B143" s="2" t="n">
+      <c r="B143" s="1" t="n">
         <v>45451</v>
       </c>
       <c r="C143" t="inlineStr">
@@ -4946,7 +4934,7 @@
       <c r="A144" t="n">
         <v>143</v>
       </c>
-      <c r="B144" s="2" t="n">
+      <c r="B144" s="1" t="n">
         <v>45753</v>
       </c>
       <c r="C144" t="inlineStr">
@@ -4978,7 +4966,7 @@
       <c r="A145" t="n">
         <v>144</v>
       </c>
-      <c r="B145" s="2" t="n">
+      <c r="B145" s="1" t="n">
         <v>45732</v>
       </c>
       <c r="C145" t="inlineStr">
@@ -5010,7 +4998,7 @@
       <c r="A146" t="n">
         <v>145</v>
       </c>
-      <c r="B146" s="2" t="n">
+      <c r="B146" s="1" t="n">
         <v>45422</v>
       </c>
       <c r="C146" t="inlineStr">
@@ -5042,7 +5030,7 @@
       <c r="A147" t="n">
         <v>146</v>
       </c>
-      <c r="B147" s="2" t="n">
+      <c r="B147" s="1" t="n">
         <v>45670</v>
       </c>
       <c r="C147" t="inlineStr">
@@ -5074,7 +5062,7 @@
       <c r="A148" t="n">
         <v>147</v>
       </c>
-      <c r="B148" s="2" t="n">
+      <c r="B148" s="1" t="n">
         <v>45648</v>
       </c>
       <c r="C148" t="inlineStr">
@@ -5106,7 +5094,7 @@
       <c r="A149" t="n">
         <v>148</v>
       </c>
-      <c r="B149" s="2" t="n">
+      <c r="B149" s="1" t="n">
         <v>45489</v>
       </c>
       <c r="C149" t="inlineStr">
@@ -5138,7 +5126,7 @@
       <c r="A150" t="n">
         <v>149</v>
       </c>
-      <c r="B150" s="2" t="n">
+      <c r="B150" s="1" t="n">
         <v>45480</v>
       </c>
       <c r="C150" t="inlineStr">
@@ -5170,7 +5158,7 @@
       <c r="A151" t="n">
         <v>150</v>
       </c>
-      <c r="B151" s="2" t="n">
+      <c r="B151" s="1" t="n">
         <v>45588</v>
       </c>
       <c r="C151" t="inlineStr">
@@ -5202,7 +5190,7 @@
       <c r="A152" t="n">
         <v>151</v>
       </c>
-      <c r="B152" s="2" t="n">
+      <c r="B152" s="1" t="n">
         <v>45497</v>
       </c>
       <c r="C152" t="inlineStr">
@@ -5234,7 +5222,7 @@
       <c r="A153" t="n">
         <v>152</v>
       </c>
-      <c r="B153" s="2" t="n">
+      <c r="B153" s="1" t="n">
         <v>45581</v>
       </c>
       <c r="C153" t="inlineStr">
@@ -5266,7 +5254,7 @@
       <c r="A154" t="n">
         <v>153</v>
       </c>
-      <c r="B154" s="2" t="n">
+      <c r="B154" s="1" t="n">
         <v>45628</v>
       </c>
       <c r="C154" t="inlineStr">
@@ -5298,7 +5286,7 @@
       <c r="A155" t="n">
         <v>154</v>
       </c>
-      <c r="B155" s="2" t="n">
+      <c r="B155" s="1" t="n">
         <v>45665</v>
       </c>
       <c r="C155" t="inlineStr">
@@ -5326,7 +5314,7 @@
       <c r="A156" t="n">
         <v>155</v>
       </c>
-      <c r="B156" s="2" t="n">
+      <c r="B156" s="1" t="n">
         <v>45616</v>
       </c>
       <c r="C156" t="inlineStr">
@@ -5358,7 +5346,7 @@
       <c r="A157" t="n">
         <v>156</v>
       </c>
-      <c r="B157" s="2" t="n">
+      <c r="B157" s="1" t="n">
         <v>45450</v>
       </c>
       <c r="C157" t="inlineStr">
@@ -5390,7 +5378,7 @@
       <c r="A158" t="n">
         <v>157</v>
       </c>
-      <c r="B158" s="2" t="n">
+      <c r="B158" s="1" t="n">
         <v>45500</v>
       </c>
       <c r="C158" t="inlineStr">
@@ -5422,7 +5410,7 @@
       <c r="A159" t="n">
         <v>158</v>
       </c>
-      <c r="B159" s="2" t="n">
+      <c r="B159" s="1" t="n">
         <v>45512</v>
       </c>
       <c r="C159" t="inlineStr">
@@ -5454,7 +5442,7 @@
       <c r="A160" t="n">
         <v>159</v>
       </c>
-      <c r="B160" s="2" t="n">
+      <c r="B160" s="1" t="n">
         <v>45500</v>
       </c>
       <c r="C160" t="inlineStr">
@@ -5486,7 +5474,7 @@
       <c r="A161" t="n">
         <v>160</v>
       </c>
-      <c r="B161" s="2" t="n">
+      <c r="B161" s="1" t="n">
         <v>45504</v>
       </c>
       <c r="C161" t="inlineStr">
@@ -5518,7 +5506,7 @@
       <c r="A162" t="n">
         <v>161</v>
       </c>
-      <c r="B162" s="2" t="n">
+      <c r="B162" s="1" t="n">
         <v>45728</v>
       </c>
       <c r="C162" t="inlineStr">
@@ -5550,7 +5538,7 @@
       <c r="A163" t="n">
         <v>162</v>
       </c>
-      <c r="B163" s="2" t="n">
+      <c r="B163" s="1" t="n">
         <v>45430</v>
       </c>
       <c r="C163" t="inlineStr">
@@ -5582,7 +5570,7 @@
       <c r="A164" t="n">
         <v>163</v>
       </c>
-      <c r="B164" s="2" t="n">
+      <c r="B164" s="1" t="n">
         <v>45512</v>
       </c>
       <c r="C164" t="inlineStr">
@@ -5614,7 +5602,7 @@
       <c r="A165" t="n">
         <v>164</v>
       </c>
-      <c r="B165" s="2" t="n">
+      <c r="B165" s="1" t="n">
         <v>45540</v>
       </c>
       <c r="C165" t="inlineStr">
@@ -5646,7 +5634,7 @@
       <c r="A166" t="n">
         <v>165</v>
       </c>
-      <c r="B166" s="2" t="n">
+      <c r="B166" s="1" t="n">
         <v>45496</v>
       </c>
       <c r="C166" t="inlineStr">
@@ -5678,7 +5666,7 @@
       <c r="A167" t="n">
         <v>166</v>
       </c>
-      <c r="B167" s="2" t="n">
+      <c r="B167" s="1" t="n">
         <v>45775</v>
       </c>
       <c r="C167" t="inlineStr">
@@ -5710,7 +5698,7 @@
       <c r="A168" t="n">
         <v>167</v>
       </c>
-      <c r="B168" s="2" t="n">
+      <c r="B168" s="1" t="n">
         <v>45486</v>
       </c>
       <c r="C168" t="inlineStr">
@@ -5742,7 +5730,7 @@
       <c r="A169" t="n">
         <v>168</v>
       </c>
-      <c r="B169" s="2" t="n">
+      <c r="B169" s="1" t="n">
         <v>45609</v>
       </c>
       <c r="C169" t="inlineStr">
@@ -5770,7 +5758,7 @@
       <c r="A170" t="n">
         <v>169</v>
       </c>
-      <c r="B170" s="2" t="n">
+      <c r="B170" s="1" t="n">
         <v>45551</v>
       </c>
       <c r="C170" t="inlineStr">
@@ -5802,7 +5790,7 @@
       <c r="A171" t="n">
         <v>170</v>
       </c>
-      <c r="B171" s="2" t="n">
+      <c r="B171" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="C171" t="inlineStr">
@@ -5830,7 +5818,7 @@
       <c r="A172" t="n">
         <v>171</v>
       </c>
-      <c r="B172" s="2" t="n">
+      <c r="B172" s="1" t="n">
         <v>45763</v>
       </c>
       <c r="C172" t="inlineStr">
@@ -5862,7 +5850,7 @@
       <c r="A173" t="n">
         <v>172</v>
       </c>
-      <c r="B173" s="2" t="n">
+      <c r="B173" s="1" t="n">
         <v>45523</v>
       </c>
       <c r="C173" t="inlineStr">
@@ -5894,7 +5882,7 @@
       <c r="A174" t="n">
         <v>173</v>
       </c>
-      <c r="B174" s="2" t="n">
+      <c r="B174" s="1" t="n">
         <v>45639</v>
       </c>
       <c r="C174" t="inlineStr">
@@ -5926,7 +5914,7 @@
       <c r="A175" t="n">
         <v>174</v>
       </c>
-      <c r="B175" s="2" t="n">
+      <c r="B175" s="1" t="n">
         <v>45486</v>
       </c>
       <c r="C175" t="inlineStr">
@@ -5958,7 +5946,7 @@
       <c r="A176" t="n">
         <v>175</v>
       </c>
-      <c r="B176" s="2" t="n">
+      <c r="B176" s="1" t="n">
         <v>45759</v>
       </c>
       <c r="C176" t="inlineStr">
@@ -5990,7 +5978,7 @@
       <c r="A177" t="n">
         <v>176</v>
       </c>
-      <c r="B177" s="2" t="n">
+      <c r="B177" s="1" t="n">
         <v>45469</v>
       </c>
       <c r="C177" t="inlineStr">
@@ -6022,7 +6010,7 @@
       <c r="A178" t="n">
         <v>177</v>
       </c>
-      <c r="B178" s="2" t="n">
+      <c r="B178" s="1" t="n">
         <v>45457</v>
       </c>
       <c r="C178" t="inlineStr">
@@ -6054,7 +6042,7 @@
       <c r="A179" t="n">
         <v>178</v>
       </c>
-      <c r="B179" s="2" t="n">
+      <c r="B179" s="1" t="n">
         <v>45664</v>
       </c>
       <c r="C179" t="inlineStr">
@@ -6086,7 +6074,7 @@
       <c r="A180" t="n">
         <v>179</v>
       </c>
-      <c r="B180" s="2" t="n">
+      <c r="B180" s="1" t="n">
         <v>45763</v>
       </c>
       <c r="C180" t="inlineStr">
@@ -6118,7 +6106,7 @@
       <c r="A181" t="n">
         <v>180</v>
       </c>
-      <c r="B181" s="2" t="n">
+      <c r="B181" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="C181" t="inlineStr">
@@ -6150,7 +6138,7 @@
       <c r="A182" t="n">
         <v>181</v>
       </c>
-      <c r="B182" s="2" t="n">
+      <c r="B182" s="1" t="n">
         <v>45600</v>
       </c>
       <c r="C182" t="inlineStr">
@@ -6180,7 +6168,7 @@
       <c r="A183" t="n">
         <v>182</v>
       </c>
-      <c r="B183" s="2" t="n">
+      <c r="B183" s="1" t="n">
         <v>45432</v>
       </c>
       <c r="C183" t="inlineStr">
@@ -6212,7 +6200,7 @@
       <c r="A184" t="n">
         <v>183</v>
       </c>
-      <c r="B184" s="2" t="n">
+      <c r="B184" s="1" t="n">
         <v>45777</v>
       </c>
       <c r="C184" t="inlineStr">
@@ -6244,7 +6232,7 @@
       <c r="A185" t="n">
         <v>184</v>
       </c>
-      <c r="B185" s="2" t="n">
+      <c r="B185" s="1" t="n">
         <v>45709</v>
       </c>
       <c r="C185" t="inlineStr">
@@ -6276,7 +6264,7 @@
       <c r="A186" t="n">
         <v>185</v>
       </c>
-      <c r="B186" s="2" t="n">
+      <c r="B186" s="1" t="n">
         <v>45710</v>
       </c>
       <c r="C186" t="inlineStr">
@@ -6308,7 +6296,7 @@
       <c r="A187" t="n">
         <v>186</v>
       </c>
-      <c r="B187" s="2" t="n">
+      <c r="B187" s="1" t="n">
         <v>45697</v>
       </c>
       <c r="C187" t="inlineStr">
@@ -6340,7 +6328,7 @@
       <c r="A188" t="n">
         <v>187</v>
       </c>
-      <c r="B188" s="2" t="n">
+      <c r="B188" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="C188" t="inlineStr">
@@ -6372,7 +6360,7 @@
       <c r="A189" t="n">
         <v>188</v>
       </c>
-      <c r="B189" s="2" t="n">
+      <c r="B189" s="1" t="n">
         <v>45762</v>
       </c>
       <c r="C189" t="inlineStr">
@@ -6404,7 +6392,7 @@
       <c r="A190" t="n">
         <v>189</v>
       </c>
-      <c r="B190" s="2" t="n">
+      <c r="B190" s="1" t="n">
         <v>45752</v>
       </c>
       <c r="C190" t="inlineStr">
@@ -6436,7 +6424,7 @@
       <c r="A191" t="n">
         <v>190</v>
       </c>
-      <c r="B191" s="2" t="n">
+      <c r="B191" s="1" t="n">
         <v>45634</v>
       </c>
       <c r="C191" t="inlineStr">
@@ -6468,7 +6456,7 @@
       <c r="A192" t="n">
         <v>191</v>
       </c>
-      <c r="B192" s="2" t="n">
+      <c r="B192" s="1" t="n">
         <v>45617</v>
       </c>
       <c r="C192" t="inlineStr">
@@ -6500,7 +6488,7 @@
       <c r="A193" t="n">
         <v>192</v>
       </c>
-      <c r="B193" s="2" t="n">
+      <c r="B193" s="1" t="n">
         <v>45631</v>
       </c>
       <c r="C193" t="inlineStr">
@@ -6528,7 +6516,7 @@
       <c r="A194" t="n">
         <v>193</v>
       </c>
-      <c r="B194" s="2" t="n">
+      <c r="B194" s="1" t="n">
         <v>45419</v>
       </c>
       <c r="C194" t="inlineStr">
@@ -6560,7 +6548,7 @@
       <c r="A195" t="n">
         <v>194</v>
       </c>
-      <c r="B195" s="2" t="n">
+      <c r="B195" s="1" t="n">
         <v>45758</v>
       </c>
       <c r="C195" t="inlineStr">
@@ -6592,7 +6580,7 @@
       <c r="A196" t="n">
         <v>195</v>
       </c>
-      <c r="B196" s="2" t="n">
+      <c r="B196" s="1" t="n">
         <v>45524</v>
       </c>
       <c r="C196" t="inlineStr">
@@ -6624,7 +6612,7 @@
       <c r="A197" t="n">
         <v>196</v>
       </c>
-      <c r="B197" s="2" t="n">
+      <c r="B197" s="1" t="n">
         <v>45568</v>
       </c>
       <c r="C197" t="inlineStr">
@@ -6656,7 +6644,7 @@
       <c r="A198" t="n">
         <v>197</v>
       </c>
-      <c r="B198" s="2" t="n">
+      <c r="B198" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="C198" t="inlineStr">
@@ -6688,7 +6676,7 @@
       <c r="A199" t="n">
         <v>198</v>
       </c>
-      <c r="B199" s="2" t="n">
+      <c r="B199" s="1" t="n">
         <v>45592</v>
       </c>
       <c r="C199" t="inlineStr">
@@ -6720,7 +6708,7 @@
       <c r="A200" t="n">
         <v>199</v>
       </c>
-      <c r="B200" s="2" t="n">
+      <c r="B200" s="1" t="n">
         <v>45521</v>
       </c>
       <c r="C200" t="inlineStr">
@@ -6752,7 +6740,7 @@
       <c r="A201" t="n">
         <v>200</v>
       </c>
-      <c r="B201" s="2" t="n">
+      <c r="B201" s="1" t="n">
         <v>45726</v>
       </c>
       <c r="C201" t="inlineStr">
